--- a/data/trans_bre/IP1003-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 2,23</t>
+          <t>-9,76; 2,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 6,82</t>
+          <t>-10,0; 6,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 10,39</t>
+          <t>-7,23; 9,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 6,27</t>
+          <t>-7,34; 5,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 205,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,85; 217,85</t>
+          <t>-83,55; 209,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,89; 353,84</t>
+          <t>-65,92; 357,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-73,94; 235,62</t>
+          <t>-77,24; 217,39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 3,19</t>
+          <t>-4,76; 3,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 6,44</t>
+          <t>-4,21; 6,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 5,21</t>
+          <t>-5,45; 4,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 5,99</t>
+          <t>-5,48; 6,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,52; 130,66</t>
+          <t>-76,11; 157,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 182,05</t>
+          <t>-53,07; 162,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-69,79; 219,29</t>
+          <t>-77,11; 179,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 195,4</t>
+          <t>-69,67; 195,24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 10,22</t>
+          <t>-2,9; 10,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 3,27</t>
+          <t>-6,1; 3,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 1,46</t>
+          <t>-7,95; 2,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,64; -0,79</t>
+          <t>-10,15; -0,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,97; 520,17</t>
+          <t>-51,58; 585,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 287,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 7,94</t>
+          <t>-8,6; 7,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 5,62</t>
+          <t>-7,54; 4,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 5,46</t>
+          <t>-8,6; 5,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 6,54</t>
+          <t>-9,83; 6,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,03; 101,4</t>
+          <t>-56,55; 110,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,62; 185,47</t>
+          <t>-79,45; 137,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-69,09; 145,59</t>
+          <t>-72,68; 127,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-90,4; 495,43</t>
+          <t>-88,34; 321,99</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 18,42</t>
+          <t>-3,2; 18,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 11,7</t>
+          <t>-6,23; 11,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 3,05</t>
+          <t>-5,32; 3,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 3,01</t>
+          <t>-21,56; 3,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,26; —</t>
+          <t>-67,58; 1012,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-75,44; 829,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,14 +1095,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,05</t>
+          <t>-100,0; 167,29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 0,86</t>
+          <t>-15,86; 0,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 2,34</t>
+          <t>-14,4; 2,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 6,89</t>
+          <t>-12,97; 5,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 8,85</t>
+          <t>-15,42; 9,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,93; 29,09</t>
+          <t>-90,12; 32,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,72; 45,97</t>
+          <t>-85,73; 68,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-79,04; 126,48</t>
+          <t>-77,74; 116,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-64,55; 80,76</t>
+          <t>-65,41; 85,28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 2,56</t>
+          <t>-5,89; 3,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 3,35</t>
+          <t>-5,0; 3,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,2</t>
+          <t>-2,71; 3,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 1,02</t>
+          <t>-13,23; 1,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-74,0; 74,53</t>
+          <t>-75,68; 111,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-71,98; 124,64</t>
+          <t>-68,37; 151,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-79,28; 333,03</t>
+          <t>-74,82; 417,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-73,65; 12,75</t>
+          <t>-73,01; 14,93</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 2,96</t>
+          <t>-5,98; 3,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 0,8</t>
+          <t>-5,87; 0,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 3,58</t>
+          <t>-3,47; 3,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 0,41</t>
+          <t>-6,4; 0,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,86; 64,34</t>
+          <t>-62,37; 68,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,57; 49,06</t>
+          <t>-81,64; 37,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-60,6; 142,52</t>
+          <t>-59,5; 138,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 35,45</t>
+          <t>-100,0; 42,11</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 1,07</t>
+          <t>-2,94; 1,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,58</t>
+          <t>-3,35; 0,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,31</t>
+          <t>-2,5; 1,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -0,28</t>
+          <t>-5,23; -0,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-38,7; 18,26</t>
+          <t>-36,68; 19,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 13,7</t>
+          <t>-47,5; 12,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 31,24</t>
+          <t>-40,26; 27,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-53,72; -3,9</t>
+          <t>-54,49; -4,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 2,1</t>
+          <t>-11,11; 1,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 6,82</t>
+          <t>-9,97; 6,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 9,67</t>
+          <t>-6,8; 10,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 5,97</t>
+          <t>-6,49; 6,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 162,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-83,55; 209,6</t>
+          <t>-79,37; 224,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-65,92; 357,0</t>
+          <t>-64,19; 389,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-77,24; 217,39</t>
+          <t>-72,15; 297,86</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 3,25</t>
+          <t>-5,17; 3,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 6,34</t>
+          <t>-4,44; 6,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 4,69</t>
+          <t>-5,11; 5,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 6,19</t>
+          <t>-5,37; 6,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-76,11; 157,4</t>
+          <t>-77,27; 176,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,07; 162,97</t>
+          <t>-58,33; 172,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-77,11; 179,34</t>
+          <t>-72,73; 217,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,67; 195,24</t>
+          <t>-64,34; 208,04</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 10,11</t>
+          <t>-2,59; 10,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 3,23</t>
+          <t>-6,32; 3,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 2,28</t>
+          <t>-8,21; 2,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -0,04</t>
+          <t>-10,69; -0,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,58; 585,18</t>
+          <t>-48,92; 656,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 287,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 7,94</t>
+          <t>-8,13; 8,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 4,84</t>
+          <t>-8,4; 4,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 5,11</t>
+          <t>-7,98; 5,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 6,07</t>
+          <t>-11,05; 5,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,55; 110,19</t>
+          <t>-56,39; 114,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,45; 137,83</t>
+          <t>-81,34; 133,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,68; 127,98</t>
+          <t>-71,04; 136,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,34; 321,99</t>
+          <t>-100,0; 320,33</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 18,22</t>
+          <t>-3,1; 17,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 11,27</t>
+          <t>-6,3; 11,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 3,13</t>
+          <t>-5,89; 3,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 3,21</t>
+          <t>-20,38; 3,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-67,58; 1012,81</t>
+          <t>-58,91; 1270,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>-78,27; 899,83</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 167,29</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 0,74</t>
+          <t>-15,78; 0,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 2,69</t>
+          <t>-14,36; 3,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 5,76</t>
+          <t>-13,28; 7,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 9,15</t>
+          <t>-16,4; 8,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,12; 32,92</t>
+          <t>-91,08; 18,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,73; 68,48</t>
+          <t>-86,65; 69,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-77,74; 116,98</t>
+          <t>-78,09; 149,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,41; 85,28</t>
+          <t>-66,15; 77,41</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 3,05</t>
+          <t>-6,09; 2,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,45</t>
+          <t>-5,26; 3,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,36</t>
+          <t>-3,04; 3,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 1,04</t>
+          <t>-13,26; 1,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-75,68; 111,93</t>
+          <t>-75,77; 84,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-68,37; 151,26</t>
+          <t>-74,11; 124,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-74,82; 417,34</t>
+          <t>-82,83; 317,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-73,01; 14,93</t>
+          <t>-71,62; 21,27</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 3,19</t>
+          <t>-5,22; 3,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,89</t>
+          <t>-6,11; 0,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 3,51</t>
+          <t>-3,83; 3,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 0,4</t>
+          <t>-6,73; 0,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 68,97</t>
+          <t>-58,36; 70,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,64; 37,61</t>
+          <t>-82,04; 30,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-59,5; 138,9</t>
+          <t>-62,56; 126,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,11</t>
+          <t>-93,12; 82,81</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,11</t>
+          <t>-3,01; 1,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,62</t>
+          <t>-3,45; 0,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,2</t>
+          <t>-2,52; 1,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -0,31</t>
+          <t>-5,46; -0,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 19,83</t>
+          <t>-37,86; 23,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 12,77</t>
+          <t>-46,73; 9,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 27,79</t>
+          <t>-40,02; 34,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-54,49; -4,34</t>
+          <t>-54,75; -2,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 1,67</t>
+          <t>-10,93; 2,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 6,81</t>
+          <t>-9,4; 6,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 10,01</t>
+          <t>-6,6; 10,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 6,55</t>
+          <t>-7,34; 7,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 162,97</t>
+          <t>-100,0; 205,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-79,37; 224,69</t>
+          <t>-81,85; 217,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,19; 389,85</t>
+          <t>-62,89; 353,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-72,15; 297,86</t>
+          <t>-69,78; 251,94</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>2,51</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 3,21</t>
+          <t>-5,7; 3,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 6,3</t>
+          <t>-4,68; 6,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 5,02</t>
+          <t>-5,08; 5,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 6,11</t>
+          <t>-3,65; 9,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-77,27; 176,3</t>
+          <t>-82,52; 130,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,33; 172,01</t>
+          <t>-59,68; 182,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,73; 217,4</t>
+          <t>-69,79; 219,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,34; 208,04</t>
+          <t>-43,29; 328,29</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,89</t>
+          <t>-5,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-82,86%</t>
+          <t>-83,22%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 10,22</t>
+          <t>-2,77; 10,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 3,25</t>
+          <t>-6,12; 3,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 2,2</t>
+          <t>-8,87; 1,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,69; -0,76</t>
+          <t>-11,17; -0,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,92; 656,16</t>
+          <t>-53,97; 520,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,37</t>
+          <t>-1,42</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-21,17%</t>
+          <t>-20,85%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 8,59</t>
+          <t>-8,63; 7,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 4,43</t>
+          <t>-7,94; 5,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 5,81</t>
+          <t>-7,56; 5,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 5,53</t>
+          <t>-10,99; 7,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,39; 114,65</t>
+          <t>-60,03; 101,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,34; 133,88</t>
+          <t>-78,62; 185,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,04; 136,95</t>
+          <t>-69,09; 145,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 320,33</t>
+          <t>-90,19; 525,05</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,82</t>
+          <t>-3,99</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-54,16%</t>
+          <t>-44,57%</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 17,53</t>
+          <t>-1,79; 18,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 11,99</t>
+          <t>-6,51; 11,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 3,12</t>
+          <t>-6,62; 3,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 3,23</t>
+          <t>-17,54; 3,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 1270,36</t>
+          <t>-48,26; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-78,27; 899,83</t>
+          <t>-75,44; 829,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 140,19</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,53</t>
+          <t>-2,96</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-14,69%</t>
+          <t>-16,36%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 0,3</t>
+          <t>-16,29; 0,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 3,11</t>
+          <t>-14,93; 2,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 7,07</t>
+          <t>-13,29; 6,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 8,41</t>
+          <t>-15,25; 8,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-91,08; 18,98</t>
+          <t>-90,93; 29,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,65; 69,97</t>
+          <t>-87,72; 45,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-78,09; 149,23</t>
+          <t>-79,04; 126,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,15; 77,41</t>
+          <t>-62,82; 76,25</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,65</t>
+          <t>-5,54</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-41,58%</t>
+          <t>-39,17%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 2,4</t>
+          <t>-5,52; 2,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 3,18</t>
+          <t>-5,01; 3,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 3,15</t>
+          <t>-2,95; 3,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 1,35</t>
+          <t>-12,96; 1,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-75,77; 84,53</t>
+          <t>-74,0; 74,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-74,11; 124,41</t>
+          <t>-71,98; 124,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-82,83; 317,06</t>
+          <t>-79,28; 333,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-71,62; 21,27</t>
+          <t>-70,49; 18,43</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-2,82</t>
+          <t>-2,76</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-64,06%</t>
+          <t>-63,48%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 3,04</t>
+          <t>-5,31; 2,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,86</t>
+          <t>-6,25; 0,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 3,48</t>
+          <t>-3,48; 3,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 0,23</t>
+          <t>-6,66; 0,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,36; 70,19</t>
+          <t>-59,86; 64,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-82,04; 30,7</t>
+          <t>-79,57; 49,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-62,56; 126,86</t>
+          <t>-60,6; 142,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-93,12; 82,81</t>
+          <t>-100,0; 42,42</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-2,29</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-33,09%</t>
+          <t>-27,34%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,37</t>
+          <t>-2,97; 1,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,43</t>
+          <t>-3,49; 0,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,37</t>
+          <t>-2,58; 1,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,46; -0,2</t>
+          <t>-4,96; 0,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 23,97</t>
+          <t>-38,7; 18,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-46,73; 9,24</t>
+          <t>-46,85; 13,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 34,68</t>
+          <t>-42,83; 31,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-54,75; -2,51</t>
+          <t>-50,05; 3,28</t>
         </is>
       </c>
     </row>
